--- a/12622343.xlsx
+++ b/12622343.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776-26271\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B108826A-2238-474B-9DDF-C7A6A5CCCEAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3D796481-EFAC-4E5D-8C52-1517A7FAF309}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="71">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -244,6 +244,15 @@
   </si>
   <si>
     <t xml:space="preserve">Day went good </t>
+  </si>
+  <si>
+    <t>Excellent</t>
+  </si>
+  <si>
+    <t>Very Satisfied</t>
+  </si>
+  <si>
+    <t>Day went splendid</t>
   </si>
 </sst>
 </file>
@@ -1482,27 +1491,51 @@
         <v>67</v>
       </c>
     </row>
-    <row r="16" spans="1:14">
-      <c r="A16" s="13"/>
-      <c r="B16" s="14"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="14"/>
-      <c r="I16" s="15" t="str">
+    <row r="16" spans="1:14" ht="15">
+      <c r="A16" s="13">
+        <v>46261</v>
+      </c>
+      <c r="B16" s="14">
+        <v>350</v>
+      </c>
+      <c r="C16" s="14">
+        <v>30</v>
+      </c>
+      <c r="D16" s="14">
+        <v>200</v>
+      </c>
+      <c r="E16" s="14">
+        <v>60</v>
+      </c>
+      <c r="F16" s="14">
+        <v>300</v>
+      </c>
+      <c r="G16" s="14">
+        <v>6</v>
+      </c>
+      <c r="H16" s="14">
+        <v>120</v>
+      </c>
+      <c r="I16" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J16" s="15" t="str">
+        <v>1060</v>
+      </c>
+      <c r="J16" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K16" s="16"/>
-      <c r="L16" s="16"/>
-      <c r="M16" s="16"/>
-      <c r="N16" s="17"/>
+        <v>380</v>
+      </c>
+      <c r="K16" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="L16" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="M16" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="N16" s="17" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13"/>

--- a/12622343.xlsx
+++ b/12622343.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776-26271\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3D796481-EFAC-4E5D-8C52-1517A7FAF309}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6A7BC8B8-A96F-4074-9AD9-D32379733805}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="71">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1537,27 +1537,51 @@
         <v>70</v>
       </c>
     </row>
-    <row r="17" spans="1:14">
-      <c r="A17" s="13"/>
-      <c r="B17" s="14"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="14"/>
-      <c r="I17" s="15" t="str">
+    <row r="17" spans="1:14" ht="15">
+      <c r="A17" s="13">
+        <v>46262</v>
+      </c>
+      <c r="B17" s="14">
+        <v>350</v>
+      </c>
+      <c r="C17" s="14">
+        <v>45</v>
+      </c>
+      <c r="D17" s="14">
+        <v>120</v>
+      </c>
+      <c r="E17" s="14">
+        <v>60</v>
+      </c>
+      <c r="F17" s="14">
+        <v>200</v>
+      </c>
+      <c r="G17" s="14">
+        <v>4</v>
+      </c>
+      <c r="H17" s="14">
+        <v>120</v>
+      </c>
+      <c r="I17" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J17" s="15" t="str">
+        <v>895</v>
+      </c>
+      <c r="J17" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K17" s="16"/>
-      <c r="L17" s="16"/>
-      <c r="M17" s="16"/>
-      <c r="N17" s="17"/>
+        <v>545</v>
+      </c>
+      <c r="K17" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="L17" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="M17" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="N17" s="17" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13"/>

--- a/12622343.xlsx
+++ b/12622343.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776-26271\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6A7BC8B8-A96F-4074-9AD9-D32379733805}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3645FF8E-0FA9-40FE-B0E3-47180DB98684}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="73">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -253,6 +253,12 @@
   </si>
   <si>
     <t>Day went splendid</t>
+  </si>
+  <si>
+    <t>It was a good day</t>
+  </si>
+  <si>
+    <t>Felt less energetic today</t>
   </si>
 </sst>
 </file>
@@ -1583,49 +1589,97 @@
         <v>67</v>
       </c>
     </row>
-    <row r="18" spans="1:14">
-      <c r="A18" s="13"/>
-      <c r="B18" s="14"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="14"/>
-      <c r="I18" s="15" t="str">
+    <row r="18" spans="1:14" ht="15">
+      <c r="A18" s="13">
+        <v>46263</v>
+      </c>
+      <c r="B18" s="14">
+        <v>420</v>
+      </c>
+      <c r="C18" s="14">
+        <v>30</v>
+      </c>
+      <c r="D18" s="14">
+        <v>200</v>
+      </c>
+      <c r="E18" s="14">
+        <v>60</v>
+      </c>
+      <c r="F18" s="14">
+        <v>0</v>
+      </c>
+      <c r="G18" s="14">
+        <v>0</v>
+      </c>
+      <c r="H18" s="14">
+        <v>200</v>
+      </c>
+      <c r="I18" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J18" s="15" t="str">
+        <v>910</v>
+      </c>
+      <c r="J18" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K18" s="16"/>
-      <c r="L18" s="16"/>
-      <c r="M18" s="16"/>
-      <c r="N18" s="17"/>
-    </row>
-    <row r="19" spans="1:14">
-      <c r="A19" s="13"/>
-      <c r="B19" s="14"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="14"/>
-      <c r="I19" s="15" t="str">
+        <v>530</v>
+      </c>
+      <c r="K18" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="L18" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="M18" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="N18" s="17" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" ht="15">
+      <c r="A19" s="13">
+        <v>46264</v>
+      </c>
+      <c r="B19" s="14">
+        <v>420</v>
+      </c>
+      <c r="C19" s="14">
+        <v>45</v>
+      </c>
+      <c r="D19" s="14">
+        <v>220</v>
+      </c>
+      <c r="E19" s="14">
+        <v>60</v>
+      </c>
+      <c r="F19" s="14">
+        <v>0</v>
+      </c>
+      <c r="G19" s="14">
+        <v>0</v>
+      </c>
+      <c r="H19" s="14">
+        <v>100</v>
+      </c>
+      <c r="I19" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J19" s="15" t="str">
+        <v>845</v>
+      </c>
+      <c r="J19" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K19" s="16"/>
-      <c r="L19" s="16"/>
-      <c r="M19" s="16"/>
-      <c r="N19" s="17"/>
+        <v>595</v>
+      </c>
+      <c r="K19" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L19" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M19" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N19" s="17" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13"/>

--- a/12622343.xlsx
+++ b/12622343.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776-26271\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3645FF8E-0FA9-40FE-B0E3-47180DB98684}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FF1E8C22-7175-4A2B-BA90-5CF86B7DF693}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="74">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -259,6 +259,9 @@
   </si>
   <si>
     <t>Felt less energetic today</t>
+  </si>
+  <si>
+    <t>Felt a little less on energy after classes today</t>
   </si>
 </sst>
 </file>
@@ -1681,27 +1684,51 @@
         <v>72</v>
       </c>
     </row>
-    <row r="20" spans="1:14">
-      <c r="A20" s="13"/>
-      <c r="B20" s="14"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="14"/>
-      <c r="I20" s="15" t="str">
+    <row r="20" spans="1:14" ht="30.75">
+      <c r="A20" s="13">
+        <v>46265</v>
+      </c>
+      <c r="B20" s="14">
+        <v>360</v>
+      </c>
+      <c r="C20" s="14">
+        <v>30</v>
+      </c>
+      <c r="D20" s="14">
+        <v>200</v>
+      </c>
+      <c r="E20" s="14">
+        <v>60</v>
+      </c>
+      <c r="F20" s="14">
+        <v>100</v>
+      </c>
+      <c r="G20" s="14">
+        <v>2</v>
+      </c>
+      <c r="H20" s="14">
+        <v>100</v>
+      </c>
+      <c r="I20" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J20" s="15" t="str">
+        <v>850</v>
+      </c>
+      <c r="J20" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K20" s="16"/>
-      <c r="L20" s="16"/>
-      <c r="M20" s="16"/>
-      <c r="N20" s="17"/>
+        <v>590</v>
+      </c>
+      <c r="K20" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L20" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M20" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N20" s="17" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="21" spans="1:14">
       <c r="A21" s="13"/>

--- a/12622343.xlsx
+++ b/12622343.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30425"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776-26271\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FF1E8C22-7175-4A2B-BA90-5CF86B7DF693}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E1BDD1BC-9E45-4696-9B39-47E769B3463F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="74">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1730,27 +1730,51 @@
         <v>73</v>
       </c>
     </row>
-    <row r="21" spans="1:14">
-      <c r="A21" s="13"/>
-      <c r="B21" s="14"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="14"/>
-      <c r="H21" s="14"/>
-      <c r="I21" s="15" t="str">
+    <row r="21" spans="1:14" ht="15">
+      <c r="A21" s="13">
+        <v>46266</v>
+      </c>
+      <c r="B21" s="14">
+        <v>360</v>
+      </c>
+      <c r="C21" s="14">
+        <v>30</v>
+      </c>
+      <c r="D21" s="14">
+        <v>200</v>
+      </c>
+      <c r="E21" s="14">
+        <v>120</v>
+      </c>
+      <c r="F21" s="14">
+        <v>250</v>
+      </c>
+      <c r="G21" s="14">
+        <v>5</v>
+      </c>
+      <c r="H21" s="14">
+        <v>120</v>
+      </c>
+      <c r="I21" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J21" s="15" t="str">
+        <v>1080</v>
+      </c>
+      <c r="J21" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K21" s="16"/>
-      <c r="L21" s="16"/>
-      <c r="M21" s="16"/>
-      <c r="N21" s="17"/>
+        <v>360</v>
+      </c>
+      <c r="K21" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L21" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M21" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="N21" s="17" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13"/>

--- a/12622343.xlsx
+++ b/12622343.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30417"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776-26271\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E1BDD1BC-9E45-4696-9B39-47E769B3463F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8491B188-5D96-4F40-A4DD-275ABCDE61FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="75">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -262,6 +262,9 @@
   </si>
   <si>
     <t>Felt a little less on energy after classes today</t>
+  </si>
+  <si>
+    <t>Tried something new today</t>
   </si>
 </sst>
 </file>
@@ -1776,27 +1779,51 @@
         <v>60</v>
       </c>
     </row>
-    <row r="22" spans="1:14">
-      <c r="A22" s="13"/>
-      <c r="B22" s="14"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="14"/>
-      <c r="I22" s="15" t="str">
+    <row r="22" spans="1:14" ht="15">
+      <c r="A22" s="13">
+        <v>46267</v>
+      </c>
+      <c r="B22" s="14">
+        <v>400</v>
+      </c>
+      <c r="C22" s="14">
+        <v>45</v>
+      </c>
+      <c r="D22" s="14">
+        <v>200</v>
+      </c>
+      <c r="E22" s="14">
+        <v>120</v>
+      </c>
+      <c r="F22" s="14">
+        <v>250</v>
+      </c>
+      <c r="G22" s="14">
+        <v>5</v>
+      </c>
+      <c r="H22" s="14">
+        <v>150</v>
+      </c>
+      <c r="I22" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J22" s="15" t="str">
+        <v>1165</v>
+      </c>
+      <c r="J22" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K22" s="16"/>
-      <c r="L22" s="16"/>
-      <c r="M22" s="16"/>
-      <c r="N22" s="17"/>
+        <v>275</v>
+      </c>
+      <c r="K22" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L22" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M22" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="N22" s="17" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="23" spans="1:14">
       <c r="A23" s="13"/>

--- a/12622343.xlsx
+++ b/12622343.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30425"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776-26271\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8491B188-5D96-4F40-A4DD-275ABCDE61FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{248A6787-C4E2-4B47-AE2B-1E8B7ABEA6DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="76">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -153,7 +153,7 @@
     <t>Month:</t>
   </si>
   <si>
-    <t>August</t>
+    <t>September</t>
   </si>
   <si>
     <t>All durations in MINUTES. Yellow cells = enter your data. Row 6 is a sample — overwrite it. Rows 2-3: fill your details.</t>
@@ -265,6 +265,9 @@
   </si>
   <si>
     <t>Tried something new today</t>
+  </si>
+  <si>
+    <t>Just as usual</t>
   </si>
 </sst>
 </file>
@@ -1825,27 +1828,51 @@
         <v>74</v>
       </c>
     </row>
-    <row r="23" spans="1:14">
-      <c r="A23" s="13"/>
-      <c r="B23" s="14"/>
-      <c r="C23" s="14"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="14"/>
-      <c r="H23" s="14"/>
-      <c r="I23" s="15" t="str">
+    <row r="23" spans="1:14" ht="15">
+      <c r="A23" s="13">
+        <v>46268</v>
+      </c>
+      <c r="B23" s="14">
+        <v>300</v>
+      </c>
+      <c r="C23" s="14">
+        <v>30</v>
+      </c>
+      <c r="D23" s="14">
+        <v>200</v>
+      </c>
+      <c r="E23" s="14">
+        <v>120</v>
+      </c>
+      <c r="F23" s="14">
+        <v>300</v>
+      </c>
+      <c r="G23" s="14">
+        <v>6</v>
+      </c>
+      <c r="H23" s="14">
+        <v>120</v>
+      </c>
+      <c r="I23" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J23" s="15" t="str">
+        <v>1070</v>
+      </c>
+      <c r="J23" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K23" s="16"/>
-      <c r="L23" s="16"/>
-      <c r="M23" s="16"/>
-      <c r="N23" s="17"/>
+        <v>370</v>
+      </c>
+      <c r="K23" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L23" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M23" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N23" s="17" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="24" spans="1:14">
       <c r="A24" s="13"/>

--- a/12622343.xlsx
+++ b/12622343.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776-26271\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{248A6787-C4E2-4B47-AE2B-1E8B7ABEA6DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C1BD68E5-9AA2-4029-A7D1-D6E67E814DA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="77">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -268,6 +268,9 @@
   </si>
   <si>
     <t>Just as usual</t>
+  </si>
+  <si>
+    <t>Took one more step towards trying something new</t>
   </si>
 </sst>
 </file>
@@ -1874,27 +1877,51 @@
         <v>75</v>
       </c>
     </row>
-    <row r="24" spans="1:14">
-      <c r="A24" s="13"/>
-      <c r="B24" s="14"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
-      <c r="I24" s="15" t="str">
+    <row r="24" spans="1:14" ht="30.75">
+      <c r="A24" s="13">
+        <v>46269</v>
+      </c>
+      <c r="B24" s="14">
+        <v>300</v>
+      </c>
+      <c r="C24" s="14">
+        <v>30</v>
+      </c>
+      <c r="D24" s="14">
+        <v>120</v>
+      </c>
+      <c r="E24" s="14">
+        <v>120</v>
+      </c>
+      <c r="F24" s="14">
+        <v>350</v>
+      </c>
+      <c r="G24" s="14">
+        <v>7</v>
+      </c>
+      <c r="H24" s="14">
+        <v>120</v>
+      </c>
+      <c r="I24" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J24" s="15" t="str">
+        <v>1040</v>
+      </c>
+      <c r="J24" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K24" s="16"/>
-      <c r="L24" s="16"/>
-      <c r="M24" s="16"/>
-      <c r="N24" s="17"/>
+        <v>400</v>
+      </c>
+      <c r="K24" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="L24" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="M24" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="N24" s="17" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="25" spans="1:14">
       <c r="A25" s="13"/>

--- a/12622343.xlsx
+++ b/12622343.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776-26271\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C1BD68E5-9AA2-4029-A7D1-D6E67E814DA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D3A9DF20-C57F-404A-B2AA-7E6454B77924}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="78">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -271,6 +271,9 @@
   </si>
   <si>
     <t>Took one more step towards trying something new</t>
+  </si>
+  <si>
+    <t>Weather felt too hot today</t>
   </si>
 </sst>
 </file>
@@ -1923,27 +1926,51 @@
         <v>76</v>
       </c>
     </row>
-    <row r="25" spans="1:14">
-      <c r="A25" s="13"/>
-      <c r="B25" s="14"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="14"/>
-      <c r="H25" s="14"/>
-      <c r="I25" s="15" t="str">
+    <row r="25" spans="1:14" ht="15">
+      <c r="A25" s="13">
+        <v>46270</v>
+      </c>
+      <c r="B25" s="14">
+        <v>400</v>
+      </c>
+      <c r="C25" s="14">
+        <v>30</v>
+      </c>
+      <c r="D25" s="14">
+        <v>240</v>
+      </c>
+      <c r="E25" s="14">
+        <v>120</v>
+      </c>
+      <c r="F25" s="14">
+        <v>50</v>
+      </c>
+      <c r="G25" s="14">
+        <v>1</v>
+      </c>
+      <c r="H25" s="14">
+        <v>180</v>
+      </c>
+      <c r="I25" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J25" s="15" t="str">
+        <v>1020</v>
+      </c>
+      <c r="J25" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K25" s="16"/>
-      <c r="L25" s="16"/>
-      <c r="M25" s="16"/>
-      <c r="N25" s="17"/>
+        <v>420</v>
+      </c>
+      <c r="K25" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L25" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M25" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="N25" s="17" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="26" spans="1:14">
       <c r="A26" s="13"/>

--- a/12622343.xlsx
+++ b/12622343.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30431"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776-26271\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D3A9DF20-C57F-404A-B2AA-7E6454B77924}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{90E7EE46-5A2B-440B-889A-22320F17AA7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="79">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -274,6 +274,9 @@
   </si>
   <si>
     <t>Weather felt too hot today</t>
+  </si>
+  <si>
+    <t>Weekend spent well</t>
   </si>
 </sst>
 </file>
@@ -1972,27 +1975,51 @@
         <v>77</v>
       </c>
     </row>
-    <row r="26" spans="1:14">
-      <c r="A26" s="13"/>
-      <c r="B26" s="14"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="14"/>
-      <c r="H26" s="14"/>
-      <c r="I26" s="15" t="str">
+    <row r="26" spans="1:14" ht="15">
+      <c r="A26" s="13">
+        <v>46271</v>
+      </c>
+      <c r="B26" s="14">
+        <v>360</v>
+      </c>
+      <c r="C26" s="14">
+        <v>45</v>
+      </c>
+      <c r="D26" s="14">
+        <v>300</v>
+      </c>
+      <c r="E26" s="14">
+        <v>120</v>
+      </c>
+      <c r="F26" s="14">
+        <v>0</v>
+      </c>
+      <c r="G26" s="14">
+        <v>0</v>
+      </c>
+      <c r="H26" s="14">
+        <v>120</v>
+      </c>
+      <c r="I26" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J26" s="15" t="str">
+        <v>945</v>
+      </c>
+      <c r="J26" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K26" s="16"/>
-      <c r="L26" s="16"/>
-      <c r="M26" s="16"/>
-      <c r="N26" s="17"/>
+        <v>495</v>
+      </c>
+      <c r="K26" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L26" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M26" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="N26" s="17" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="27" spans="1:14">
       <c r="A27" s="13"/>
